--- a/Diagrama de Gantt IAVE.xlsx
+++ b/Diagrama de Gantt IAVE.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="301">
   <si>
     <t>Escriba el nombre de la compañía en la celda B2.</t>
   </si>
@@ -1020,6 +1020,9 @@
   </si>
   <si>
     <t>Ya no se realiza este ajuste por recomendación de gerencia</t>
+  </si>
+  <si>
+    <t>Tarea de sistemas</t>
   </si>
 </sst>
 </file>
@@ -2838,9 +2841,6 @@
     <xf numFmtId="171" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2855,6 +2855,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -10437,10 +10440,10 @@
   <sheetData>
     <row r="1" spans="1:361" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1"/>
-      <c r="B1" s="236" t="s">
+      <c r="B1" s="235" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="236"/>
+      <c r="C1" s="235"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="4"/>
@@ -10454,38 +10457,38 @@
       <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="236" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="237"/>
+      <c r="C2" s="236"/>
       <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:361" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="238" t="s">
+      <c r="B3" s="237" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="239" t="s">
+      <c r="C3" s="237"/>
+      <c r="D3" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="240"/>
-      <c r="F3" s="235">
+      <c r="E3" s="239"/>
+      <c r="F3" s="240">
         <v>45714</v>
       </c>
-      <c r="G3" s="235"/>
+      <c r="G3" s="240"/>
     </row>
     <row r="4" spans="1:361" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="53"/>
-      <c r="D4" s="239" t="s">
+      <c r="D4" s="238" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="240"/>
+      <c r="E4" s="239"/>
       <c r="F4" s="6">
         <v>49</v>
       </c>
@@ -49937,7 +49940,9 @@
       <c r="H104" s="216" t="s">
         <v>279</v>
       </c>
-      <c r="I104" s="216"/>
+      <c r="I104" s="216" t="s">
+        <v>300</v>
+      </c>
       <c r="J104" s="11"/>
       <c r="K104" s="11"/>
       <c r="L104" s="15"/>
@@ -50679,7 +50684,9 @@
       <c r="H106" s="216" t="s">
         <v>279</v>
       </c>
-      <c r="I106" s="216"/>
+      <c r="I106" s="216" t="s">
+        <v>300</v>
+      </c>
       <c r="J106" s="11"/>
       <c r="K106" s="11"/>
       <c r="L106" s="15"/>
@@ -53997,50 +54004,6 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="MC4:MI4"/>
-    <mergeCell ref="MJ4:MP4"/>
-    <mergeCell ref="MQ4:MW4"/>
-    <mergeCell ref="KT4:KZ4"/>
-    <mergeCell ref="LA4:LG4"/>
-    <mergeCell ref="LH4:LN4"/>
-    <mergeCell ref="LO4:LU4"/>
-    <mergeCell ref="LV4:MB4"/>
-    <mergeCell ref="JK4:JQ4"/>
-    <mergeCell ref="JR4:JX4"/>
-    <mergeCell ref="JY4:KE4"/>
-    <mergeCell ref="KF4:KL4"/>
-    <mergeCell ref="KM4:KS4"/>
-    <mergeCell ref="IB4:IH4"/>
-    <mergeCell ref="II4:IO4"/>
-    <mergeCell ref="IP4:IV4"/>
-    <mergeCell ref="IW4:JC4"/>
-    <mergeCell ref="JD4:JJ4"/>
-    <mergeCell ref="GS4:GY4"/>
-    <mergeCell ref="GZ4:HF4"/>
-    <mergeCell ref="HG4:HM4"/>
-    <mergeCell ref="HN4:HT4"/>
-    <mergeCell ref="HU4:IA4"/>
-    <mergeCell ref="FJ4:FP4"/>
-    <mergeCell ref="FQ4:FW4"/>
-    <mergeCell ref="FX4:GD4"/>
-    <mergeCell ref="GE4:GK4"/>
-    <mergeCell ref="GL4:GR4"/>
-    <mergeCell ref="EA4:EG4"/>
-    <mergeCell ref="EH4:EN4"/>
-    <mergeCell ref="EO4:EU4"/>
-    <mergeCell ref="EV4:FB4"/>
-    <mergeCell ref="FC4:FI4"/>
-    <mergeCell ref="DT4:DZ4"/>
-    <mergeCell ref="CK4:CQ4"/>
-    <mergeCell ref="CR4:CX4"/>
-    <mergeCell ref="CY4:DE4"/>
-    <mergeCell ref="DF4:DL4"/>
-    <mergeCell ref="DM4:DS4"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="CD4:CJ4"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="L4:R4"/>
@@ -54053,6 +54016,50 @@
     <mergeCell ref="BI4:BO4"/>
     <mergeCell ref="BP4:BV4"/>
     <mergeCell ref="BW4:CC4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="DT4:DZ4"/>
+    <mergeCell ref="CK4:CQ4"/>
+    <mergeCell ref="CR4:CX4"/>
+    <mergeCell ref="CY4:DE4"/>
+    <mergeCell ref="DF4:DL4"/>
+    <mergeCell ref="DM4:DS4"/>
+    <mergeCell ref="EA4:EG4"/>
+    <mergeCell ref="EH4:EN4"/>
+    <mergeCell ref="EO4:EU4"/>
+    <mergeCell ref="EV4:FB4"/>
+    <mergeCell ref="FC4:FI4"/>
+    <mergeCell ref="FJ4:FP4"/>
+    <mergeCell ref="FQ4:FW4"/>
+    <mergeCell ref="FX4:GD4"/>
+    <mergeCell ref="GE4:GK4"/>
+    <mergeCell ref="GL4:GR4"/>
+    <mergeCell ref="GS4:GY4"/>
+    <mergeCell ref="GZ4:HF4"/>
+    <mergeCell ref="HG4:HM4"/>
+    <mergeCell ref="HN4:HT4"/>
+    <mergeCell ref="HU4:IA4"/>
+    <mergeCell ref="IB4:IH4"/>
+    <mergeCell ref="II4:IO4"/>
+    <mergeCell ref="IP4:IV4"/>
+    <mergeCell ref="IW4:JC4"/>
+    <mergeCell ref="JD4:JJ4"/>
+    <mergeCell ref="JK4:JQ4"/>
+    <mergeCell ref="JR4:JX4"/>
+    <mergeCell ref="JY4:KE4"/>
+    <mergeCell ref="KF4:KL4"/>
+    <mergeCell ref="KM4:KS4"/>
+    <mergeCell ref="MC4:MI4"/>
+    <mergeCell ref="MJ4:MP4"/>
+    <mergeCell ref="MQ4:MW4"/>
+    <mergeCell ref="KT4:KZ4"/>
+    <mergeCell ref="LA4:LG4"/>
+    <mergeCell ref="LH4:LN4"/>
+    <mergeCell ref="LO4:LU4"/>
+    <mergeCell ref="LV4:MB4"/>
   </mergeCells>
   <conditionalFormatting sqref="E113:E114 E24:E28 E31:E33 E7:E22 E38 E36 E41:E43 E61:E86 E47:E58">
     <cfRule type="dataBar" priority="982">
